--- a/World-Builds/Reformed-Zurich-and-Geneva/Lexicon_Deployment_Index.xlsx
+++ b/World-Builds/Reformed-Zurich-and-Geneva/Lexicon_Deployment_Index.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1065,7 +1065,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>None -- jointly authored across the strand boundary, the opposite of single-source concentration</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>Meaning</t>
@@ -2031,11 +2035,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Predestination, Election, Providence, Disputation, Sola Scriptura, The Sixty-Seven Articles, Sign and the Thing Signified, Spiritual Presence, Mutual Consent, Consistory, Excommunication, Antistes, Elder, Heads of Agreement</t>
+          <t>Predestination, Election, Providence, Disputation, Sola Scriptura, The Sixty-Seven Articles, The Lord's Supper, Sign and the Thing Signified, Spiritual Presence, Mutual Consent, Consistory, Excommunication, Antistes, Elder, Heads of Agreement</t>
         </is>
       </c>
     </row>
@@ -2061,11 +2065,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Memorial / Commemoration, Mutual Consent</t>
+          <t>The Lord's Supper, Memorial / Commemoration, Mutual Consent</t>
         </is>
       </c>
     </row>
